--- a/public/exports-with-coowners/29189404.xlsx
+++ b/public/exports-with-coowners/29189404.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014098</t>
+          <t xml:space="preserve">200014104</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311608660</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">

--- a/public/exports-with-coowners/29189404.xlsx
+++ b/public/exports-with-coowners/29189404.xlsx
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agerskellet 13</t>
+          <t xml:space="preserve">Frederiksborgvej 561</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568845</t>
+          <t xml:space="preserve">2178448</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023910</t>
+          <t xml:space="preserve">200023938</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,40 +10691,40 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 561</t>
+          <t xml:space="preserve">Grantoften 3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178448</t>
+          <t xml:space="preserve">2217322</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023938</t>
+          <t xml:space="preserve">200024857</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 3</t>
+          <t xml:space="preserve">Grantoften 5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J144">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 5</t>
+          <t xml:space="preserve">Hyrdehøj 62</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217322</t>
+          <t xml:space="preserve">9113193</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>392</v>
+        <v>722</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024857</t>
+          <t xml:space="preserve">200024858</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 62</t>
+          <t xml:space="preserve">Kornvej 1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113193</t>
+          <t xml:space="preserve">8550293</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>722</v>
+        <v>812</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024858</t>
+          <t xml:space="preserve">200024855</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kornvej 1</t>
+          <t xml:space="preserve">Dommervænget 30</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550293</t>
+          <t xml:space="preserve">5306255</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>812</v>
+        <v>1225</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024855</t>
+          <t xml:space="preserve">200024872</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2019-12-02</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dommervænget 30</t>
+          <t xml:space="preserve">Bygaden 28</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306255</t>
+          <t xml:space="preserve">2178710</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>1225</v>
+        <v>263</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024872</t>
+          <t xml:space="preserve">200024953</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-02</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28</t>
+          <t xml:space="preserve">Gammel Darupvej 3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178710</t>
+          <t xml:space="preserve">5307880</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>263</v>
+        <v>1383</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024953</t>
+          <t xml:space="preserve">200024956</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Darupvej 3</t>
+          <t xml:space="preserve">Lysalleen 33</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307880</t>
+          <t xml:space="preserve">8717244</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>1383</v>
+        <v>1298</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024956</t>
+          <t xml:space="preserve">200024948</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysalleen 33</t>
+          <t xml:space="preserve">Eriksvej 40C</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,20 +11301,20 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8717244</t>
+          <t xml:space="preserve">5308364</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J151">
-        <v>1298</v>
+        <v>852</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024948</t>
+          <t xml:space="preserve">200024993</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 40C</t>
+          <t xml:space="preserve">Københavnsvej 106C</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308364</t>
+          <t xml:space="preserve">7896055</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>852</v>
+        <v>680</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024993</t>
+          <t xml:space="preserve">200024994</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 106C</t>
+          <t xml:space="preserve">Kamstrupsti 2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896055</t>
+          <t xml:space="preserve">5308151</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>680</v>
+        <v>400</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024994</t>
+          <t xml:space="preserve">200027969</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupsti 2</t>
+          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,30 +11526,30 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308151</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J154">
-        <v>400</v>
+        <v>995</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027969</t>
+          <t xml:space="preserve">200030999</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">BALSLEV</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2020-05-03</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
+          <t xml:space="preserve">Astersvej 9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,30 +11601,30 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">5308975</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>995</v>
+        <v>4292</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030999</t>
+          <t xml:space="preserve">200049549</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALSLEV</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-03</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 9</t>
+          <t xml:space="preserve">Stændertorvet 1D</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308975</t>
+          <t xml:space="preserve">5304086</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>4292</v>
+        <v>1906</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049549</t>
+          <t xml:space="preserve">200050785</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2021-06-29</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 1D</t>
+          <t xml:space="preserve">Mosestykket 21</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304086</t>
+          <t xml:space="preserve">2208892</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J157">
-        <v>1906</v>
+        <v>770</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050785</t>
+          <t xml:space="preserve">200051688</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-29</t>
+          <t xml:space="preserve">2021-08-03</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosestykket 21</t>
+          <t xml:space="preserve">Københavnsvej 266</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,30 +11826,30 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208892</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>770</v>
+        <v>573</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051688</t>
+          <t xml:space="preserve">200057196</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Forum r.i.</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-03</t>
+          <t xml:space="preserve">2022-02-06</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266</t>
+          <t xml:space="preserve">Møllehusvej 13</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">8135053</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,21 +11910,21 @@
         </is>
       </c>
       <c r="J159">
-        <v>573</v>
+        <v>9546</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057196</t>
+          <t xml:space="preserve">200057529</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forum r.i.</t>
+          <t xml:space="preserve">TopDahl ApS</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-06</t>
+          <t xml:space="preserve">2022-02-20</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 13</t>
+          <t xml:space="preserve">Herregårdsvej 42</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8135053</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>9546</v>
+        <v>1898</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057529</t>
+          <t xml:space="preserve">200057621</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-20</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 42</t>
+          <t xml:space="preserve">Tranevej 7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">7938930</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,21 +12060,21 @@
         </is>
       </c>
       <c r="J161">
-        <v>1898</v>
+        <v>638</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057621</t>
+          <t xml:space="preserve">200060567</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">TopDahl ApS</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 7</t>
+          <t xml:space="preserve">Baunegårdsvej 80</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,30 +12126,30 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938930</t>
+          <t xml:space="preserve">2179645</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060567</t>
+          <t xml:space="preserve">311052501</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-29</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,40 +12191,40 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 80</t>
+          <t xml:space="preserve">Højbakken 2</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179645</t>
+          <t xml:space="preserve">10229610</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J163">
-        <v>677</v>
+        <v>620</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311052501</t>
+          <t xml:space="preserve">311060924</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12281,11 +12281,11 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J164">
-        <v>620</v>
+        <v>1226</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbakken 2</t>
+          <t xml:space="preserve">Baunehøjvej 5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,30 +12351,30 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">10229610</t>
+          <t xml:space="preserve">2174626</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>1226</v>
+        <v>287</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311060924</t>
+          <t xml:space="preserve">311082107</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-23</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 5</t>
+          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174626</t>
+          <t xml:space="preserve">5309424</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>287</v>
+        <v>2196</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082107</t>
+          <t xml:space="preserve">311082106</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
+          <t xml:space="preserve">Himmelev Bygade 22C</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309424</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J167">
-        <v>2196</v>
+        <v>426</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082106</t>
+          <t xml:space="preserve">311082104</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 22C</t>
+          <t xml:space="preserve">Bistruphøj 2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">5312115</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>426</v>
+        <v>1048</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082104</t>
+          <t xml:space="preserve">311083539</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistruphøj 2</t>
+          <t xml:space="preserve">Bistrupvænge 16</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,25 +12651,25 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312115</t>
+          <t xml:space="preserve">5312015</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="J169">
-        <v>1048</v>
+        <v>927</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083539</t>
+          <t xml:space="preserve">311083529</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvænge 16</t>
+          <t xml:space="preserve">Lindegårdsparken 1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">139</t>
         </is>
       </c>
       <c r="J170">
-        <v>927</v>
+        <v>20718</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsparken 1</t>
+          <t xml:space="preserve">Nygade 13</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,30 +12801,30 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312015</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>20718</v>
+        <v>568</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083529</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-14</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 13</t>
+          <t xml:space="preserve">Nygade 14</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 14</t>
+          <t xml:space="preserve">Nygade 18</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J173">
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 18</t>
+          <t xml:space="preserve">Rosenhaven 13</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J174">
-        <v>568</v>
+        <v>268</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311098182</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 13</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2174669</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>268</v>
+        <v>401</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098182</t>
+          <t xml:space="preserve">311101306</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-03-17</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Sankt Ols Stræde 5</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174669</t>
+          <t xml:space="preserve">5303417</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101306</t>
+          <t xml:space="preserve">311109494</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-17</t>
+          <t xml:space="preserve">2025-04-28</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 5</t>
+          <t xml:space="preserve">Strandgade 2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303417</t>
+          <t xml:space="preserve">5312664, 100884612</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J177">
-        <v>482</v>
+        <v>345</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109494</t>
+          <t xml:space="preserve">311110647</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-28</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 2</t>
+          <t xml:space="preserve">Lammegade 26</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312664, 100884612</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J178">
-        <v>345</v>
+        <v>667</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110647</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 26</t>
+          <t xml:space="preserve">Lammegade 28</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J179">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 28</t>
+          <t xml:space="preserve">Lammegade 30</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J180">
-        <v>667</v>
+        <v>496</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 30</t>
+          <t xml:space="preserve">Lammegade 36</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13556,11 +13556,11 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J181">
-        <v>496</v>
+        <v>624</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 36</t>
+          <t xml:space="preserve">Vestergade 6A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">5312565</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>624</v>
+        <v>3282</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311115034</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 6A</t>
+          <t xml:space="preserve">Lyngbakken 1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312565</t>
+          <t xml:space="preserve">7175316</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>3282</v>
+        <v>362</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115034</t>
+          <t xml:space="preserve">311118205</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakken 1</t>
+          <t xml:space="preserve">Navervej 16</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7175316</t>
+          <t xml:space="preserve">2209531</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>362</v>
+        <v>1432</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118205</t>
+          <t xml:space="preserve">311124782</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-10</t>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J185">
-        <v>1432</v>
+        <v>979</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navervej 16</t>
+          <t xml:space="preserve">Rabalderstræde 16</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209531</t>
+          <t xml:space="preserve">719145, 100067704</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,21 +13935,21 @@
         </is>
       </c>
       <c r="J186">
-        <v>979</v>
+        <v>3529</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124782</t>
+          <t xml:space="preserve">311137096</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-13</t>
+          <t xml:space="preserve">2025-09-28</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 16</t>
+          <t xml:space="preserve">Jernbanegade 21A</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,30 +14001,30 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">719145, 100067704</t>
+          <t xml:space="preserve">8995769</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>3529</v>
+        <v>1236</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311137096</t>
+          <t xml:space="preserve">311162791</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-28</t>
+          <t xml:space="preserve">2026-03-07</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14051,12 +14051,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskilde Kommune</t>
+          <t xml:space="preserve">I/S ROSKILDE III</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 21A</t>
+          <t xml:space="preserve">Stationscentret 1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995769</t>
+          <t xml:space="preserve">258583, 258584, 258585, 258586, 258587, 258588, 258589, 258590</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,31 +14085,31 @@
         </is>
       </c>
       <c r="J188">
-        <v>1236</v>
+        <v>988</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311162791</t>
+          <t xml:space="preserve">311240411</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-07</t>
+          <t xml:space="preserve">2027-04-10</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -14126,12 +14126,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">I/S ROSKILDE III</t>
+          <t xml:space="preserve">Roskilde Kommune</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationscentret 1</t>
+          <t xml:space="preserve">Vestre Hedevej 32</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,30 +14151,30 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">258583, 258584, 258585, 258586, 258587, 258588, 258589, 258590</t>
+          <t xml:space="preserve">719290, 100013803</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J189">
-        <v>988</v>
+        <v>276</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311240411</t>
+          <t xml:space="preserve">311241595</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-10</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Hedevej 32</t>
+          <t xml:space="preserve">Basgangen 20</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,20 +14226,20 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">719290, 100013803</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="J190">
-        <v>276</v>
+        <v>2980</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241595</t>
+          <t xml:space="preserve">311351867</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2028-12-17</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basgangen 20</t>
+          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,30 +14301,30 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">100122346</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>2980</v>
+        <v>9549</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351867</t>
+          <t xml:space="preserve">311522399</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-17</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,40 +14366,40 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
+          <t xml:space="preserve">Søndergade 11</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">100122346</t>
+          <t xml:space="preserve">7855029</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J192">
-        <v>9549</v>
+        <v>1530</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522399</t>
+          <t xml:space="preserve">311552201</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,40 +14441,40 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 11</t>
+          <t xml:space="preserve">Sandhøjsvej 4</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">7855029</t>
+          <t xml:space="preserve">1304635</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>1530</v>
+        <v>599</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552201</t>
+          <t xml:space="preserve">311569226</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandhøjsvej 4</t>
+          <t xml:space="preserve">Ramsømaglevej 17B</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304635</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>599</v>
+        <v>1459</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569226</t>
+          <t xml:space="preserve">311570325</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17B</t>
+          <t xml:space="preserve">Ramsømaglevej 17D</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14606,15 +14606,15 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J195">
-        <v>1459</v>
+        <v>355</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570325</t>
+          <t xml:space="preserve">311570327</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,40 +14666,40 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17D</t>
+          <t xml:space="preserve">Ejboparken 6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J196">
-        <v>355</v>
+        <v>435</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570327</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6</t>
+          <t xml:space="preserve">Ejboparken 6B</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14831,11 +14831,11 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J198">
-        <v>517</v>
+        <v>258</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6B</t>
+          <t xml:space="preserve">Ejboparken 8A</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14906,11 +14906,11 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J199">
-        <v>258</v>
+        <v>477</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 8A</t>
+          <t xml:space="preserve">Hørhusene 61</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,20 +14976,20 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">5312139</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J200">
-        <v>477</v>
+        <v>826</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311595512</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørhusene 61</t>
+          <t xml:space="preserve">Københavnsvej 266C</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,30 +15051,30 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312139</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J201">
-        <v>826</v>
+        <v>322</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595512</t>
+          <t xml:space="preserve">311587049</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-22</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,40 +15116,40 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266C</t>
+          <t xml:space="preserve">Bueager 8</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">2211135</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J202">
-        <v>322</v>
+        <v>469</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587049</t>
+          <t xml:space="preserve">311608657</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">2032-06-17</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 8</t>
+          <t xml:space="preserve">Bueager 2</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15206,15 +15206,15 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>469</v>
+        <v>4564</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311610029</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-17</t>
+          <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15281,11 +15281,11 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J204">
-        <v>4564</v>
+        <v>2127</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15356,11 +15356,11 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J205">
-        <v>2127</v>
+        <v>847</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 2</t>
+          <t xml:space="preserve">Bueager 6</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15431,15 +15431,15 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J206">
-        <v>847</v>
+        <v>1898</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610029</t>
+          <t xml:space="preserve">311610041</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,40 +15491,40 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 6</t>
+          <t xml:space="preserve">Køgevej 106</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211135</t>
+          <t xml:space="preserve">5308417</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J207">
-        <v>1898</v>
+        <v>1620</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610041</t>
+          <t xml:space="preserve">311626283</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-23</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,40 +15566,40 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køgevej 106</t>
+          <t xml:space="preserve">Snoldelev Bygade 21B</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308417</t>
+          <t xml:space="preserve">2202050</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>1620</v>
+        <v>438</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626283</t>
+          <t xml:space="preserve">311633105</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,17 +15641,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snoldelev Bygade 21B</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202050</t>
+          <t xml:space="preserve">2170541</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>438</v>
+        <v>1257</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633105</t>
+          <t xml:space="preserve">311633102</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170541</t>
+          <t xml:space="preserve">8016122</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,21 +15735,21 @@
         </is>
       </c>
       <c r="J210">
-        <v>1257</v>
+        <v>2104</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633102</t>
+          <t xml:space="preserve">311645050</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-04</t>
+          <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15806,11 +15806,11 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J211">
-        <v>2104</v>
+        <v>434</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
+          <t xml:space="preserve">Gundsølillevej 2</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,30 +15876,30 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8016122</t>
+          <t xml:space="preserve">2167605</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>434</v>
+        <v>979</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645050</t>
+          <t xml:space="preserve">311643576</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-08</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 2</t>
+          <t xml:space="preserve">Gundsølillevej 6</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15956,15 +15956,15 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J213">
-        <v>979</v>
+        <v>4101</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643576</t>
+          <t xml:space="preserve">311643577</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 6</t>
+          <t xml:space="preserve">Sognevej 50</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167605</t>
+          <t xml:space="preserve">2172270</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J214">
-        <v>4101</v>
+        <v>3519</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643577</t>
+          <t xml:space="preserve">311644570</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 50</t>
+          <t xml:space="preserve">Planetvej 30</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172270</t>
+          <t xml:space="preserve">8907547</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,21 +16110,21 @@
         </is>
       </c>
       <c r="J215">
-        <v>3519</v>
+        <v>897</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644570</t>
+          <t xml:space="preserve">311644810</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">BOTJEK A/S</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-23</t>
+          <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J216">
-        <v>897</v>
+        <v>398</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J217">
-        <v>398</v>
+        <v>1311</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J218">
-        <v>1311</v>
+        <v>924</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16406,11 +16406,11 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J219">
-        <v>924</v>
+        <v>487</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -16481,11 +16481,11 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J220">
-        <v>487</v>
+        <v>256</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J221">
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J222">
-        <v>256</v>
+        <v>897</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J223">
-        <v>897</v>
+        <v>983</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J224">
-        <v>983</v>
+        <v>552</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16856,11 +16856,11 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J225">
-        <v>552</v>
+        <v>897</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J226">
@@ -17006,11 +17006,11 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J227">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -17081,11 +17081,11 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J228">
-        <v>898</v>
+        <v>280</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -17156,11 +17156,11 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J229">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -17231,11 +17231,11 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J230">
-        <v>900</v>
+        <v>789</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -17291,40 +17291,40 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planetvej 30</t>
+          <t xml:space="preserve">H H Kochs Vej 4</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8907547</t>
+          <t xml:space="preserve">2173007</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J231">
-        <v>789</v>
+        <v>7796</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644810</t>
+          <t xml:space="preserve">311645058</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTJEK A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-24</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">H H Kochs Vej 4</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173007</t>
+          <t xml:space="preserve">2180519</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,16 +17385,16 @@
         </is>
       </c>
       <c r="J232">
-        <v>7796</v>
+        <v>1448</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645058</t>
+          <t xml:space="preserve">311644999</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -17456,11 +17456,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J233">
-        <v>1448</v>
+        <v>413</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Lindelunden 1</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180519</t>
+          <t xml:space="preserve">5306821</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,21 +17535,21 @@
         </is>
       </c>
       <c r="J234">
-        <v>413</v>
+        <v>5829</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644999</t>
+          <t xml:space="preserve">311645727</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindelunden 1</t>
+          <t xml:space="preserve">Trekroner Centervej 41</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17606,11 +17606,11 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>5829</v>
+        <v>12072</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17666,17 +17666,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Centervej 41</t>
+          <t xml:space="preserve">Ramsømaglevej 19</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306821</t>
+          <t xml:space="preserve">2213437</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -17685,11 +17685,11 @@
         </is>
       </c>
       <c r="J236">
-        <v>12072</v>
+        <v>2744</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645727</t>
+          <t xml:space="preserve">311646168</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17756,15 +17756,15 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J237">
-        <v>2744</v>
+        <v>1287</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646168</t>
+          <t xml:space="preserve">311646167</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17816,30 +17816,30 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 19</t>
+          <t xml:space="preserve">Gammel Vindingevej 10</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213437</t>
+          <t xml:space="preserve">2209330</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J238">
-        <v>1287</v>
+        <v>5956</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646167</t>
+          <t xml:space="preserve">311646682</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17906,15 +17906,15 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J239">
-        <v>5956</v>
+        <v>447</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646682</t>
+          <t xml:space="preserve">311646683</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Vindingevej 10</t>
+          <t xml:space="preserve">Margrethekær 2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,20 +17976,20 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209330</t>
+          <t xml:space="preserve">9700889</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J240">
-        <v>447</v>
+        <v>2442</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646683</t>
+          <t xml:space="preserve">311647649</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 2</t>
+          <t xml:space="preserve">Margrethekær 10</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18056,15 +18056,15 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J241">
-        <v>2442</v>
+        <v>1500</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647649</t>
+          <t xml:space="preserve">311647742</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 10</t>
+          <t xml:space="preserve">Margrethekær 12</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 12</t>
+          <t xml:space="preserve">Margrethekær 4</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18206,11 +18206,11 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J243">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 4</t>
+          <t xml:space="preserve">Margrethekær 6</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18281,11 +18281,11 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J244">
-        <v>1514</v>
+        <v>1500</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 6</t>
+          <t xml:space="preserve">Margrethekær 8</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18356,11 +18356,11 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J245">
-        <v>1500</v>
+        <v>1577</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 8</t>
+          <t xml:space="preserve">Hyrdehøj 3</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,30 +18426,30 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700889</t>
+          <t xml:space="preserve">7713101</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J246">
-        <v>1577</v>
+        <v>11744</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647742</t>
+          <t xml:space="preserve">311649946</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18506,15 +18506,15 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J247">
-        <v>11744</v>
+        <v>1185</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649946</t>
+          <t xml:space="preserve">311649970</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2032-12-18</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 3</t>
+          <t xml:space="preserve">Møllehusvej 118</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,30 +18576,30 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7713101</t>
+          <t xml:space="preserve">258624, 258625</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J248">
-        <v>1185</v>
+        <v>4232</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649970</t>
+          <t xml:space="preserve">311650857</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-18</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,17 +18641,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 118</t>
+          <t xml:space="preserve">Kirkebjergvej 2</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">258624, 258625</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -18660,11 +18660,11 @@
         </is>
       </c>
       <c r="J249">
-        <v>4232</v>
+        <v>1786</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650857</t>
+          <t xml:space="preserve">311652564</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 2</t>
+          <t xml:space="preserve">Kirkebjergvej 4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18731,15 +18731,15 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J250">
-        <v>1786</v>
+        <v>1585</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652564</t>
+          <t xml:space="preserve">311652563</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 4</t>
+          <t xml:space="preserve">Kirkebjergvej 6</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18806,15 +18806,15 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J251">
-        <v>1585</v>
+        <v>2239</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652563</t>
+          <t xml:space="preserve">311652567</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 6</t>
+          <t xml:space="preserve">Kirkebjergvej 8</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18881,15 +18881,15 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J252">
-        <v>2239</v>
+        <v>610</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652567</t>
+          <t xml:space="preserve">311652565</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18941,40 +18941,40 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 8</t>
+          <t xml:space="preserve">Ørstedvej 63B</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>610</v>
+        <v>8368</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652565</t>
+          <t xml:space="preserve">311652748</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-01-06</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,40 +19016,40 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63B</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J254">
-        <v>8368</v>
+        <v>1815</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652748</t>
+          <t xml:space="preserve">311652906</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-06</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19106,11 +19106,11 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J255">
-        <v>1815</v>
+        <v>2850</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -19181,11 +19181,11 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J256">
-        <v>2850</v>
+        <v>1908</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -19241,40 +19241,40 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">5304953</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>1908</v>
+        <v>6173</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652906</t>
+          <t xml:space="preserve">311656342</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
+          <t xml:space="preserve">Københavnsvej 34</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304953</t>
+          <t xml:space="preserve">5311321</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -19335,21 +19335,21 @@
         </is>
       </c>
       <c r="J258">
-        <v>6173</v>
+        <v>9899</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656342</t>
+          <t xml:space="preserve">311655694</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 34</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,25 +19401,25 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311321</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J259">
-        <v>9899</v>
+        <v>9084</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655694</t>
+          <t xml:space="preserve">311655558</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Bymarken 37</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,20 +19476,20 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5306248</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>9084</v>
+        <v>8569</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655558</t>
+          <t xml:space="preserve">311656548</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymarken 37</t>
+          <t xml:space="preserve">Gormsvej 9B</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,20 +19551,20 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306248</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J261">
-        <v>8569</v>
+        <v>440</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656548</t>
+          <t xml:space="preserve">311656782</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 9B</t>
+          <t xml:space="preserve">Rådhusbuen 3</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J262">
-        <v>440</v>
+        <v>5709</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656782</t>
+          <t xml:space="preserve">311657131</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-30</t>
+          <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 3</t>
+          <t xml:space="preserve">Munkebro 2</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,20 +19701,20 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5303415</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J263">
-        <v>5709</v>
+        <v>608</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657131</t>
+          <t xml:space="preserve">311657447</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-31</t>
+          <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkebro 2</t>
+          <t xml:space="preserve">Sankt Ols Stræde 3</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19781,15 +19781,15 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J264">
-        <v>608</v>
+        <v>858</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657447</t>
+          <t xml:space="preserve">311657449</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19856,15 +19856,15 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J265">
-        <v>858</v>
+        <v>433</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657449</t>
+          <t xml:space="preserve">311657448</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 3</t>
+          <t xml:space="preserve">Absalonsgade 1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303415</t>
+          <t xml:space="preserve">8995768</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,21 +19935,21 @@
         </is>
       </c>
       <c r="J266">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657448</t>
+          <t xml:space="preserve">311659172</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-01</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 1</t>
+          <t xml:space="preserve">Absalonsgade 2</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20006,11 +20006,11 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J267">
-        <v>378</v>
+        <v>6187</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 2</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995768</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -20085,21 +20085,21 @@
         </is>
       </c>
       <c r="J268">
-        <v>6187</v>
+        <v>9651</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659172</t>
+          <t xml:space="preserve">311666198</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-14</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,17 +20141,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Baunegårdsvej 85</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,21 +20160,21 @@
         </is>
       </c>
       <c r="J269">
-        <v>9651</v>
+        <v>3340</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666198</t>
+          <t xml:space="preserve">311664732</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-14</t>
+          <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20231,11 +20231,11 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J270">
-        <v>3340</v>
+        <v>916</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -20306,11 +20306,11 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J271">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -20381,11 +20381,11 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J272">
-        <v>900</v>
+        <v>711</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -20456,11 +20456,11 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J273">
-        <v>711</v>
+        <v>1816</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -20516,30 +20516,30 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 85</t>
+          <t xml:space="preserve">Lynghøjen 107A</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J274">
-        <v>1816</v>
+        <v>817</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664732</t>
+          <t xml:space="preserve">311665647</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-07</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107A</t>
+          <t xml:space="preserve">Lynghøjen 107B</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20606,15 +20606,15 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J275">
-        <v>817</v>
+        <v>1552</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665647</t>
+          <t xml:space="preserve">311665669</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107B</t>
+          <t xml:space="preserve">Lynghøjen 107C</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20681,11 +20681,11 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J276">
-        <v>1552</v>
+        <v>433</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107C</t>
+          <t xml:space="preserve">Lynghøjen 107</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20756,15 +20756,15 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J277">
-        <v>433</v>
+        <v>12308</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665669</t>
+          <t xml:space="preserve">311666274</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-03-14</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107</t>
+          <t xml:space="preserve">Industrileddet 4</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">2180546</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -20835,21 +20835,21 @@
         </is>
       </c>
       <c r="J278">
-        <v>12308</v>
+        <v>2200</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666274</t>
+          <t xml:space="preserve">311666541</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-14</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrileddet 4</t>
+          <t xml:space="preserve">Ollerupvej 5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180546</t>
+          <t xml:space="preserve">2173759</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -20910,21 +20910,21 @@
         </is>
       </c>
       <c r="J279">
-        <v>2200</v>
+        <v>12044</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666541</t>
+          <t xml:space="preserve">311667669</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-03-20</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20981,11 +20981,11 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J280">
-        <v>12044</v>
+        <v>494</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 5</t>
+          <t xml:space="preserve">Ollerupvej 7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -21056,15 +21056,15 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J281">
-        <v>494</v>
+        <v>826</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667669</t>
+          <t xml:space="preserve">311667621</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 7</t>
+          <t xml:space="preserve">Helligkorsvej 42A</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21126,20 +21126,20 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173759</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J282">
-        <v>826</v>
+        <v>3137</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667621</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-20</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21206,11 +21206,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J283">
-        <v>3137</v>
+        <v>6340</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21281,11 +21281,11 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J284">
-        <v>6340</v>
+        <v>2165</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42A</t>
+          <t xml:space="preserve">Helligkorsvej 42C</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21356,11 +21356,11 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J285">
-        <v>2165</v>
+        <v>778</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42C</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,20 +21426,20 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J286">
-        <v>778</v>
+        <v>2177</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21506,11 +21506,11 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J287">
-        <v>2177</v>
+        <v>3318</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -21581,11 +21581,11 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J288">
-        <v>3318</v>
+        <v>766</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Østre Vindingevej 221C</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21656,15 +21656,15 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J289">
-        <v>766</v>
+        <v>2100</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670926</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221C</t>
+          <t xml:space="preserve">Bistrup Bakke 5</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -21726,30 +21726,30 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">100513814</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">109</t>
         </is>
       </c>
       <c r="J290">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670926</t>
+          <t xml:space="preserve">311673245</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 5</t>
+          <t xml:space="preserve">Bistrup Bakke 3</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21806,15 +21806,15 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">109</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J291">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673245</t>
+          <t xml:space="preserve">311675948</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 3</t>
+          <t xml:space="preserve">Bistrup Bakke 7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -21881,15 +21881,15 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J292">
-        <v>997</v>
+        <v>1077</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675948</t>
+          <t xml:space="preserve">311675950</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 7</t>
+          <t xml:space="preserve">Astersvej 15</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21951,30 +21951,30 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513814</t>
+          <t xml:space="preserve">8995869</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J293">
-        <v>1077</v>
+        <v>10347</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675950</t>
+          <t xml:space="preserve">311676003</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-24</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22031,11 +22031,11 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J294">
-        <v>10347</v>
+        <v>6038</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15</t>
+          <t xml:space="preserve">Astersvej 15C</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22106,15 +22106,15 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J295">
-        <v>6038</v>
+        <v>643</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676003</t>
+          <t xml:space="preserve">311676217</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22166,30 +22166,30 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15C</t>
+          <t xml:space="preserve">Ørstedvej 63A</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995869</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J296">
-        <v>643</v>
+        <v>585</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676217</t>
+          <t xml:space="preserve">311679099</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,30 +22241,30 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63A</t>
+          <t xml:space="preserve">Kongebakken 19</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>585</v>
+        <v>6671</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679099</t>
+          <t xml:space="preserve">311683094</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-25</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19</t>
+          <t xml:space="preserve">Kongebakken 19A</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">9306001</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -22335,11 +22335,11 @@
         </is>
       </c>
       <c r="J298">
-        <v>6671</v>
+        <v>630</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683094</t>
+          <t xml:space="preserve">311683580</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-25</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19A</t>
+          <t xml:space="preserve">Trekroner Alle 1</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306001</t>
+          <t xml:space="preserve">2174448</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -22410,11 +22410,11 @@
         </is>
       </c>
       <c r="J299">
-        <v>630</v>
+        <v>1216</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683580</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-26</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -22481,11 +22481,11 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J300">
-        <v>1216</v>
+        <v>1537</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -22556,11 +22556,11 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J301">
-        <v>1537</v>
+        <v>962</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -22631,11 +22631,11 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J302">
-        <v>962</v>
+        <v>3144</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -22706,11 +22706,11 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J303">
-        <v>3144</v>
+        <v>929</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -22781,11 +22781,11 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J304">
-        <v>929</v>
+        <v>553</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
@@ -22856,11 +22856,11 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J305">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -22931,15 +22931,15 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J306">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725441</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -23006,15 +23006,15 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J307">
-        <v>599</v>
+        <v>715</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725441</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1</t>
+          <t xml:space="preserve">Trekroner Alle 1C</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J308">
-        <v>715</v>
+        <v>2011</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725438</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23126,12 +23126,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskilde Kommune</t>
+          <t xml:space="preserve">Boligselskabet Sjælland</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1C</t>
+          <t xml:space="preserve">Jernbanegade 62A</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -23151,30 +23151,30 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174448</t>
+          <t xml:space="preserve">262555, 262556</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J309">
-        <v>2011</v>
+        <v>1283</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725438</t>
+          <t xml:space="preserve">311731744</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-01-04</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23201,12 +23201,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Sjælland</t>
+          <t xml:space="preserve">Roskilde Kommune</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 62A</t>
+          <t xml:space="preserve">Piledyssen 50</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">262555, 262556</t>
+          <t xml:space="preserve">2172114</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -23235,21 +23235,21 @@
         </is>
       </c>
       <c r="J310">
-        <v>1283</v>
+        <v>595</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731744</t>
+          <t xml:space="preserve">311743780</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-04</t>
+          <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23276,12 +23276,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskilde Kommune</t>
+          <t xml:space="preserve">Naturstyrelsen</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledyssen 50</t>
+          <t xml:space="preserve">Boserupvej 86</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -23301,30 +23301,30 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172114</t>
+          <t xml:space="preserve">719284, 7739559</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J311">
-        <v>595</v>
+        <v>322</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743780</t>
+          <t xml:space="preserve">311751178</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-07</t>
+          <t xml:space="preserve">2034-04-11</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -23351,12 +23351,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturstyrelsen</t>
+          <t xml:space="preserve">Roskilde Kommune</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boserupvej 86</t>
+          <t xml:space="preserve">Vindeboder 7</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -23376,30 +23376,30 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">719284, 7739559</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J312">
-        <v>322</v>
+        <v>686</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751178</t>
+          <t xml:space="preserve">311787742</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-11</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23456,11 +23456,11 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J313">
-        <v>686</v>
+        <v>452</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -23531,15 +23531,15 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J314">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787742</t>
+          <t xml:space="preserve">311787741</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -23606,15 +23606,15 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J315">
-        <v>479</v>
+        <v>310</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787741</t>
+          <t xml:space="preserve">311787745</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 7</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -23676,30 +23676,30 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J316">
-        <v>310</v>
+        <v>470</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787745</t>
+          <t xml:space="preserve">311793891</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Margrethevej 5</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -23751,30 +23751,30 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">2171290</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J317">
-        <v>470</v>
+        <v>379</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793891</t>
+          <t xml:space="preserve">311827298</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-28</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 5</t>
+          <t xml:space="preserve">Kamstrupvej 1A</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171290</t>
+          <t xml:space="preserve">2170150</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -23835,21 +23835,21 @@
         </is>
       </c>
       <c r="J318">
-        <v>379</v>
+        <v>1122</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827298</t>
+          <t xml:space="preserve">311827519</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupvej 1A</t>
+          <t xml:space="preserve">Store Valbyvej 248B</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170150</t>
+          <t xml:space="preserve">2179764</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23910,21 +23910,21 @@
         </is>
       </c>
       <c r="J319">
-        <v>1122</v>
+        <v>6510</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827519</t>
+          <t xml:space="preserve">311836213</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 248B</t>
+          <t xml:space="preserve">Baunehøjvej 9</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,20 +23976,20 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179764</t>
+          <t xml:space="preserve">2174627</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J320">
-        <v>6510</v>
+        <v>410</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836213</t>
+          <t xml:space="preserve">311842230</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-07-02</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 9</t>
+          <t xml:space="preserve">Poppelgårdsvej 8</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,30 +24051,30 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174627</t>
+          <t xml:space="preserve">100072983</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J321">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842230</t>
+          <t xml:space="preserve">311846096</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-02</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelgårdsvej 8</t>
+          <t xml:space="preserve">Bredgade 17B</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">100072983</t>
+          <t xml:space="preserve">5303694</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -24135,11 +24135,11 @@
         </is>
       </c>
       <c r="J322">
-        <v>280</v>
+        <v>982</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846096</t>
+          <t xml:space="preserve">311848390</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-24</t>
+          <t xml:space="preserve">2035-08-11</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 17B</t>
+          <t xml:space="preserve">Ringstedgade 16</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303694</t>
+          <t xml:space="preserve">5303892</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -24210,11 +24210,11 @@
         </is>
       </c>
       <c r="J323">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848390</t>
+          <t xml:space="preserve">311848394</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 16</t>
+          <t xml:space="preserve">Ringstedgade 22</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303892</t>
+          <t xml:space="preserve">10239664</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -24285,11 +24285,11 @@
         </is>
       </c>
       <c r="J324">
-        <v>938</v>
+        <v>300</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848394</t>
+          <t xml:space="preserve">311848392</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 22</t>
+          <t xml:space="preserve">Margrethevej 7</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">10239664</t>
+          <t xml:space="preserve">2171297</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -24360,21 +24360,21 @@
         </is>
       </c>
       <c r="J325">
-        <v>300</v>
+        <v>8868</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848392</t>
+          <t xml:space="preserve">311848839</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-11</t>
+          <t xml:space="preserve">2035-08-13</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 7</t>
+          <t xml:space="preserve">Østre Kirkevej 7</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -24426,7 +24426,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171297</t>
+          <t xml:space="preserve">2173901</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -24435,21 +24435,21 @@
         </is>
       </c>
       <c r="J326">
-        <v>8868</v>
+        <v>858</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848839</t>
+          <t xml:space="preserve">311871119</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-13</t>
+          <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,40 +24491,40 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kirkevej 7</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173901</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J327">
-        <v>858</v>
+        <v>1249</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871119</t>
+          <t xml:space="preserve">311878552</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-27</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -24566,40 +24566,40 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Lises Markvej 2</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">100513466</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J328">
-        <v>1249</v>
+        <v>1387</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878552</t>
+          <t xml:space="preserve">311890892</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-03-27</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -24641,17 +24641,17 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lises Markvej 2</t>
+          <t xml:space="preserve">Hyldevænget 2</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513466</t>
+          <t xml:space="preserve">2213558</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -24660,21 +24660,21 @@
         </is>
       </c>
       <c r="J329">
-        <v>1387</v>
+        <v>530</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890892</t>
+          <t xml:space="preserve">311922906</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-27</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -24716,17 +24716,17 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldevænget 2</t>
+          <t xml:space="preserve">Maglehøjen 6</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213558</t>
+          <t xml:space="preserve">5307587</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -24735,11 +24735,11 @@
         </is>
       </c>
       <c r="J330">
-        <v>530</v>
+        <v>1934</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922906</t>
+          <t xml:space="preserve">311925372</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglehøjen 6</t>
+          <t xml:space="preserve">Engbækvej 20</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -24801,30 +24801,30 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307587</t>
+          <t xml:space="preserve">9808161</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J331">
-        <v>1934</v>
+        <v>821</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925372</t>
+          <t xml:space="preserve">311928726</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -24866,30 +24866,30 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbækvej 20</t>
+          <t xml:space="preserve">Agerskellet 13</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808161</t>
+          <t xml:space="preserve">7568845</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J332">
-        <v>821</v>
+        <v>354</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928726</t>
+          <t xml:space="preserve">311931597</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-29</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
